--- a/ClueLayout/ClueLayoutMarked.xlsx
+++ b/ClueLayout/ClueLayoutMarked.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rocki\Desktop\Clue Repo\ClueRepo\ClueLayout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F34BC3F-70BE-4929-8B0B-F5C960A1DDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1293615C-9B56-4551-8FA4-DDC7A3F0C5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{88D44900-2CB3-4386-A592-6E0FBA31EB14}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{88D44900-2CB3-4386-A592-6E0FBA31EB14}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -160,7 +160,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -227,6 +227,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -240,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -252,6 +258,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -645,7 +652,7 @@
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="11" t="s">
         <v>36</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1030,7 +1037,7 @@
       <c r="P7" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="Q7" s="4" t="s">
+      <c r="Q7" s="10" t="s">
         <v>0</v>
       </c>
       <c r="R7" s="4" t="s">
@@ -1181,7 +1188,7 @@
       <c r="U9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="V9" s="2" t="s">
+      <c r="V9" s="11" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1234,7 +1241,7 @@
       <c r="P10" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="Q10" s="4" t="s">
+      <c r="Q10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="R10" s="4" t="s">
@@ -1328,7 +1335,7 @@
       <c r="B12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="10" t="s">
         <v>32</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -1535,10 +1542,10 @@
       <c r="C15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="2" t="s">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -1902,7 +1909,7 @@
       <c r="L20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M20" s="5" t="s">
+      <c r="M20" s="2" t="s">
         <v>1</v>
       </c>
       <c r="N20" s="4" t="s">
@@ -1937,7 +1944,7 @@
       <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="11" t="s">
         <v>34</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -1946,7 +1953,7 @@
       <c r="D21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="10" t="s">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="s">
@@ -1961,7 +1968,7 @@
       <c r="I21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J21" s="6" t="s">
+      <c r="J21" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K21" s="1" t="s">
@@ -1979,7 +1986,7 @@
       <c r="O21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="P21" s="4" t="s">
+      <c r="P21" s="10" t="s">
         <v>0</v>
       </c>
       <c r="Q21" s="1" t="s">
@@ -2133,7 +2140,7 @@
       <c r="U23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V23" s="2" t="s">
+      <c r="V23" s="11" t="s">
         <v>37</v>
       </c>
     </row>
